--- a/public/downloads/SmithAtmosphere2025.xlsx
+++ b/public/downloads/SmithAtmosphere2025.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -656,10 +679,10 @@
         <v>6</v>
       </c>
       <c r="N3" s="5">
-        <v>11.12764573097229</v>
+        <v>11127.64573097229</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03566553118901375</v>
+        <v>35.66553118901375</v>
       </c>
       <c r="P3" s="5">
         <v>312</v>
@@ -706,10 +729,10 @@
         <v>6</v>
       </c>
       <c r="N4" s="5">
-        <v>40.98744201660156</v>
+        <v>40987.44201660156</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04549105662219929</v>
+        <v>45.4910566221993</v>
       </c>
       <c r="P4" s="5">
         <v>901</v>
@@ -756,10 +779,10 @@
         <v>6</v>
       </c>
       <c r="N5" s="5">
-        <v>184.9322681427002</v>
+        <v>184932.2681427002</v>
       </c>
       <c r="O5" s="4">
-        <v>0.50945528413967</v>
+        <v>509.45528413967</v>
       </c>
       <c r="P5" s="5">
         <v>363</v>
@@ -806,10 +829,10 @@
         <v>6</v>
       </c>
       <c r="N6" s="5">
-        <v>37.56348919868469</v>
+        <v>37563.48919868469</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09206737548697229</v>
+        <v>92.0673754869723</v>
       </c>
       <c r="P6" s="5">
         <v>408</v>
@@ -856,10 +879,10 @@
         <v>6</v>
       </c>
       <c r="N7" s="5">
-        <v>46.18692135810852</v>
+        <v>46186.92135810852</v>
       </c>
       <c r="O7" s="4">
-        <v>0.181125181796504</v>
+        <v>181.125181796504</v>
       </c>
       <c r="P7" s="5">
         <v>255</v>
@@ -906,10 +929,10 @@
         <v>6</v>
       </c>
       <c r="N8" s="5">
-        <v>4.227220058441162</v>
+        <v>4227.220058441162</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01329314483786529</v>
+        <v>13.29314483786529</v>
       </c>
       <c r="P8" s="5">
         <v>318</v>
@@ -956,10 +979,10 @@
         <v>6</v>
       </c>
       <c r="N9" s="5">
-        <v>14.81958413124084</v>
+        <v>14819.58413124084</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03207702192909274</v>
+        <v>32.07702192909274</v>
       </c>
       <c r="P9" s="5">
         <v>462</v>
@@ -1006,10 +1029,10 @@
         <v>6</v>
       </c>
       <c r="N10" s="5">
-        <v>30.89933252334595</v>
+        <v>30899.33252334595</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08853676940786805</v>
+        <v>88.53676940786805</v>
       </c>
       <c r="P10" s="5">
         <v>349</v>
@@ -1056,10 +1079,10 @@
         <v>6</v>
       </c>
       <c r="N11" s="5">
-        <v>15.20385718345642</v>
+        <v>15203.85718345642</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04258783524777709</v>
+        <v>42.58783524777709</v>
       </c>
       <c r="P11" s="5">
         <v>357</v>
@@ -1106,10 +1129,10 @@
         <v>6</v>
       </c>
       <c r="N12" s="5">
-        <v>8.310263395309448</v>
+        <v>8310.263395309448</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01969256728746315</v>
+        <v>19.69256728746315</v>
       </c>
       <c r="P12" s="5">
         <v>422</v>
@@ -1156,10 +1179,10 @@
         <v>6</v>
       </c>
       <c r="N13" s="5">
-        <v>27.82423853874207</v>
+        <v>27824.23853874207</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07602250966869417</v>
+        <v>76.02250966869417</v>
       </c>
       <c r="P13" s="5">
         <v>366</v>
@@ -1206,10 +1229,10 @@
         <v>6</v>
       </c>
       <c r="N14" s="5">
-        <v>22.26354813575745</v>
+        <v>22263.54813575745</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2393929907070693</v>
+        <v>239.3929907070693</v>
       </c>
       <c r="P14" s="5">
         <v>93</v>
@@ -1256,10 +1279,10 @@
         <v>6</v>
       </c>
       <c r="N15" s="5">
-        <v>84.44817233085632</v>
+        <v>84448.17233085632</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2469244804995799</v>
+        <v>246.9244804995799</v>
       </c>
       <c r="P15" s="5">
         <v>342</v>
@@ -1306,10 +1329,10 @@
         <v>6</v>
       </c>
       <c r="N16" s="5">
-        <v>10.61494994163513</v>
+        <v>10614.94994163513</v>
       </c>
       <c r="O16" s="4">
-        <v>0.101094761348906</v>
+        <v>101.094761348906</v>
       </c>
       <c r="P16" s="5">
         <v>105</v>
@@ -1356,10 +1379,10 @@
         <v>6</v>
       </c>
       <c r="N17" s="5">
-        <v>37.84346795082092</v>
+        <v>37843.46795082092</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09778673889101014</v>
+        <v>97.78673889101015</v>
       </c>
       <c r="P17" s="5">
         <v>387</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,25 +1494,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08755302320981002</v>
+        <v>0.2791019106613206</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08755302320981002</v>
+        <v>0.2791019106613206</v>
       </c>
       <c r="D3" s="4">
-        <v>0.0916831998740804</v>
+        <v>0.2506868935490942</v>
       </c>
       <c r="E3" s="4">
-        <v>90.76190476190477</v>
+        <v>94.26530612244898</v>
       </c>
       <c r="F3" s="4">
-        <v>94.51006711409396</v>
+        <v>96.54362416107382</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -1498,25 +1553,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2791019106613206</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1427294138103753</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1427294138103753</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.05941427164409419</v>
+        <v>0.3384378580340854</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05941427164409419</v>
+        <v>0.3384378580340854</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09455837512322596</v>
+        <v>0.6501350968061637</v>
       </c>
       <c r="E4" s="4">
-        <v>89.48979591836735</v>
+        <v>93.06122448979592</v>
       </c>
       <c r="F4" s="4">
-        <v>92.28187919463087</v>
+        <v>95.26845637583892</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1539,9 +1612,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3384378580340854</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3384378580340854</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1641,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1660,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1702,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,37 +1733,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1472598940651878</v>
+        <v>1.131594308252686</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1472598940651878</v>
+        <v>0.7342142536621115</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1537514597695335</v>
+        <v>1.185978539820069</v>
       </c>
       <c r="E3" s="4">
-        <v>94.36734693877551</v>
+        <v>86.87755102040816</v>
       </c>
       <c r="F3" s="4">
-        <v>95.20134228187919</v>
+        <v>91.25503355704699</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -1668,27 +1790,45 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6661573512712365</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.158974505618751</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9349788381875019</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9590655732275195</v>
+        <v>0.1624041962743945</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9590655732275195</v>
+        <v>0.1624041962743945</v>
       </c>
       <c r="D4" s="4">
-        <v>1.145184652817363</v>
+        <v>0.2658816743017383</v>
       </c>
       <c r="E4" s="4">
-        <v>92.04081632653062</v>
+        <v>87.85714285714286</v>
       </c>
       <c r="F4" s="4">
-        <v>92.01342281879195</v>
+        <v>90.1006711409396</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1711,9 +1851,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1624041962743945</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1624041962743945</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1880,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1899,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1941,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,67 +1972,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2292433352949203</v>
+        <v>0.08755302320981002</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2292433352949203</v>
+        <v>0.08755302320981002</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1986762288032182</v>
+        <v>0.0916831998740804</v>
       </c>
       <c r="E3" s="4">
-        <v>84.86394557823128</v>
+        <v>90.76190476190477</v>
       </c>
       <c r="F3" s="4">
+        <v>94.51006711409396</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.05109513207551118</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08096511075257411</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08096511075257411</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.05941427164409419</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.05941427164409419</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.09455837512322596</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.48979591836735</v>
+      </c>
+      <c r="F4" s="4">
         <v>92.28187919463087</v>
       </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.003746168625469</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.003746168625469</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.072217123520488</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.31972789115646</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.74496644295301</v>
-      </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
@@ -1883,9 +2090,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05941427164409419</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05941427164409419</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2119,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2138,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2180,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,25 +2211,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1849022967973596</v>
+        <v>0.1472598940651878</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1849022967973596</v>
+        <v>0.1472598940651878</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1732556445756799</v>
+        <v>0.1537514597695335</v>
       </c>
       <c r="E3" s="4">
-        <v>93.83673469387755</v>
+        <v>94.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>95.76510067114094</v>
+        <v>95.20134228187919</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2014,25 +2270,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01502551005688844</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1502649960765655</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1502649960765655</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5849620270849414</v>
+        <v>0.9590655732275195</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5849620270849414</v>
+        <v>0.9590655732275195</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7932998108984179</v>
+        <v>1.145184652817363</v>
       </c>
       <c r="E4" s="4">
-        <v>93.67346938775511</v>
+        <v>92.04081632653062</v>
       </c>
       <c r="F4" s="4">
-        <v>95.57046979865771</v>
+        <v>92.01342281879195</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2055,9 +2329,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9590655732275195</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9590655732275195</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2358,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2377,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2419,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,25 +2450,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.84338024689349</v>
+        <v>0.2292433352949203</v>
       </c>
       <c r="C3" s="4">
-        <v>0.84338024689349</v>
+        <v>0.2292433352949203</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8435271842637903</v>
+        <v>0.1986762288032182</v>
       </c>
       <c r="E3" s="4">
-        <v>99.87755102040816</v>
+        <v>84.86394557823128</v>
       </c>
       <c r="F3" s="4">
-        <v>99.48322147651007</v>
+        <v>92.28187919463087</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2186,25 +2509,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0858382327714807</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2120756887406242</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2120756887406242</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3064676356195246</v>
+        <v>1.003746168625469</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3064676356195246</v>
+        <v>1.003746168625469</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2908583712452906</v>
+        <v>1.072217123520488</v>
       </c>
       <c r="E4" s="4">
-        <v>100</v>
+        <v>84.31972789115646</v>
       </c>
       <c r="F4" s="4">
-        <v>99.93288590604027</v>
+        <v>91.74496644295301</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2227,9 +2568,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.003746168625469</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.003746168625469</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2597,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2605,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2616,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2658,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,25 +2689,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7854401691118127</v>
+        <v>0.1849022967973596</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7854401691118127</v>
+        <v>0.1849022967973596</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7873785598436243</v>
+        <v>0.1732556445756799</v>
       </c>
       <c r="E3" s="4">
-        <v>91.38775510204081</v>
+        <v>93.83673469387755</v>
       </c>
       <c r="F3" s="4">
-        <v>95.30201342281879</v>
+        <v>95.76510067114094</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2358,37 +2748,55 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1849022967973596</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09631816026406341</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09631816026406341</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.662198202622065</v>
+        <v>0.5849620270849414</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.5849620270849414</v>
       </c>
       <c r="D4" s="4">
-        <v>2.800285475266108</v>
+        <v>0.7932998108984179</v>
       </c>
       <c r="E4" s="4">
-        <v>90.61224489795919</v>
+        <v>93.67346938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>94.49664429530202</v>
+        <v>95.57046979865771</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2397,11 +2805,27 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5849620270849414</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5849620270849414</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2836,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2855,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2897,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,25 +2928,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2785952271677544</v>
+        <v>0.84338024689349</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2785952271677544</v>
+        <v>0.84338024689349</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2754166545130303</v>
+        <v>0.8435271842637903</v>
       </c>
       <c r="E3" s="4">
-        <v>99.51020408163265</v>
+        <v>99.87755102040816</v>
       </c>
       <c r="F3" s="4">
-        <v>99.22147651006712</v>
+        <v>99.48322147651007</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2530,25 +2987,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.84338024689349</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0686221217753433</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0686221217753433</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2157207560415468</v>
+        <v>0.3064676356195246</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2157207560415468</v>
+        <v>0.3064676356195246</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2055405211328303</v>
+        <v>0.2908583712452906</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
       </c>
       <c r="F4" s="4">
-        <v>99.86577181208054</v>
+        <v>99.93288590604027</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2571,9 +3046,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3064676356195246</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3064676356195246</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3075,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3094,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3136,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,25 +3167,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6560295684495813</v>
+        <v>0.7854401691118127</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6560295684495813</v>
+        <v>0.7854401691118127</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6656717879930383</v>
+        <v>0.7873785598436243</v>
       </c>
       <c r="E3" s="4">
-        <v>87.81632653061224</v>
+        <v>91.38775510204081</v>
       </c>
       <c r="F3" s="4">
-        <v>93.56375838926175</v>
+        <v>95.30201342281879</v>
       </c>
       <c r="G3" s="5">
         <v>5</v>
@@ -2702,37 +3226,53 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7854401691118127</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05362727280014723</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05362727280014723</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4435326027990669</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4435326027990669</v>
-      </c>
+        <v>2.662198202622065</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.5552879738928169</v>
+        <v>2.800285475266108</v>
       </c>
       <c r="E4" s="4">
-        <v>88.06122448979592</v>
+        <v>90.61224489795919</v>
       </c>
       <c r="F4" s="4">
-        <v>94.36241610738254</v>
+        <v>94.49664429530202</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2741,11 +3281,25 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.662198202622065</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3310,1348 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2785952271677544</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2785952271677544</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2754166545130303</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.51020408163265</v>
+      </c>
+      <c r="F3" s="4">
+        <v>99.22147651006712</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2647695763269312</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1486653125727776</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1486653125727776</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2157207560415468</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2157207560415468</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2055405211328303</v>
+      </c>
+      <c r="E4" s="4">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4">
+        <v>99.86577181208054</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2157207560415468</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2157207560415468</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6560295684495813</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6560295684495813</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6656717879930383</v>
+      </c>
+      <c r="E3" s="4">
+        <v>87.81632653061224</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.56375838926175</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6560295684495813</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.114965831009913</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.114965831009913</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4435326027990669</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4435326027990669</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5552879738928169</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.06122448979592</v>
+      </c>
+      <c r="F4" s="4">
+        <v>94.36241610738254</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4435326027990669</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4435326027990669</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3089196202804336</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3089196202804336</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3200325486709366</v>
+      </c>
+      <c r="K3" s="4">
+        <v>95.17006802721087</v>
+      </c>
+      <c r="L3" s="4">
+        <v>95.78299776286354</v>
+      </c>
+      <c r="M3" s="5">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>11127.64573097229</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.66553118901375</v>
+      </c>
+      <c r="P3" s="5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5198319884305853</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2171477635052543</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3692090550008172</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.5215419501136</v>
+      </c>
+      <c r="L4" s="4">
+        <v>81.99105145414002</v>
+      </c>
+      <c r="M4" s="5">
+        <v>6</v>
+      </c>
+      <c r="N4" s="5">
+        <v>40987.44201660156</v>
+      </c>
+      <c r="O4" s="4">
+        <v>45.4910566221993</v>
+      </c>
+      <c r="P4" s="5">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3473683007175628</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3473683007175628</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3535284646634049</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.62925170068026</v>
+      </c>
+      <c r="L5" s="4">
+        <v>93.46196868008947</v>
+      </c>
+      <c r="M5" s="5">
+        <v>6</v>
+      </c>
+      <c r="N5" s="5">
+        <v>184932.2681427002</v>
+      </c>
+      <c r="O5" s="4">
+        <v>509.45528413967</v>
+      </c>
+      <c r="P5" s="5">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3384833983856628</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3384833983856628</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3553168626902689</v>
+      </c>
+      <c r="K6" s="4">
+        <v>88.58843537414965</v>
+      </c>
+      <c r="L6" s="4">
+        <v>91.96868008948545</v>
+      </c>
+      <c r="M6" s="5">
+        <v>6</v>
+      </c>
+      <c r="N6" s="5">
+        <v>37563.48919868469</v>
+      </c>
+      <c r="O6" s="4">
+        <v>92.0673754869723</v>
+      </c>
+      <c r="P6" s="5">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.161493506790688</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.161493506790688</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1647115218256815</v>
+      </c>
+      <c r="K7" s="4">
+        <v>95.52721088435374</v>
+      </c>
+      <c r="L7" s="4">
+        <v>97.08612975391499</v>
+      </c>
+      <c r="M7" s="5">
+        <v>6</v>
+      </c>
+      <c r="N7" s="5">
+        <v>46186.92135810852</v>
+      </c>
+      <c r="O7" s="4">
+        <v>181.125181796504</v>
+      </c>
+      <c r="P7" s="5">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1753474878476603</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1753474878476603</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2060518305052728</v>
+      </c>
+      <c r="K8" s="4">
+        <v>94.06462585034014</v>
+      </c>
+      <c r="L8" s="4">
+        <v>96.33109619686799</v>
+      </c>
+      <c r="M8" s="5">
+        <v>6</v>
+      </c>
+      <c r="N8" s="5">
+        <v>4227.220058441162</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.29314483786529</v>
+      </c>
+      <c r="P8" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.992879454061358</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7804639098048805</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1.044232590759763</v>
+      </c>
+      <c r="K9" s="4">
+        <v>87.04081632653062</v>
+      </c>
+      <c r="L9" s="4">
+        <v>91.06263982102907</v>
+      </c>
+      <c r="M9" s="5">
+        <v>6</v>
+      </c>
+      <c r="N9" s="5">
+        <v>14819.58413124084</v>
+      </c>
+      <c r="O9" s="4">
+        <v>32.07702192909274</v>
+      </c>
+      <c r="P9" s="5">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.07737330423449412</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.07737330423449412</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.08364654040301946</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.5498866213152</v>
+      </c>
+      <c r="L10" s="4">
+        <v>94.13870246085011</v>
+      </c>
+      <c r="M10" s="5">
+        <v>6</v>
+      </c>
+      <c r="N10" s="5">
+        <v>30899.33252334595</v>
+      </c>
+      <c r="O10" s="4">
+        <v>88.53676940786805</v>
+      </c>
+      <c r="P10" s="5">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2850650922683911</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2850650922683911</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3214945769536532</v>
+      </c>
+      <c r="K11" s="4">
+        <v>93.9795918367347</v>
+      </c>
+      <c r="L11" s="4">
+        <v>94.67002237136467</v>
+      </c>
+      <c r="M11" s="5">
+        <v>6</v>
+      </c>
+      <c r="N11" s="5">
+        <v>15203.85718345642</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.58783524777709</v>
+      </c>
+      <c r="P11" s="5">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3440207687214316</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3440207687214316</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.3295948552285931</v>
+      </c>
+      <c r="K12" s="4">
+        <v>84.7732426303855</v>
+      </c>
+      <c r="L12" s="4">
+        <v>92.19239373601791</v>
+      </c>
+      <c r="M12" s="5">
+        <v>6</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8310.263395309448</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.69256728746315</v>
+      </c>
+      <c r="P12" s="5">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1777588047342097</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1777588047342097</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2116352238015925</v>
+      </c>
+      <c r="K13" s="4">
+        <v>93.80952380952381</v>
+      </c>
+      <c r="L13" s="4">
+        <v>95.73266219239373</v>
+      </c>
+      <c r="M13" s="5">
+        <v>6</v>
+      </c>
+      <c r="N13" s="5">
+        <v>27824.23853874207</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.02250966869417</v>
+      </c>
+      <c r="P13" s="5">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1082630407493735</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1082630407493735</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1056637417952877</v>
+      </c>
+      <c r="K14" s="4">
+        <v>99.89795918367346</v>
+      </c>
+      <c r="L14" s="4">
+        <v>99.55816554809844</v>
+      </c>
+      <c r="M14" s="5">
+        <v>6</v>
+      </c>
+      <c r="N14" s="5">
+        <v>22263.54813575745</v>
+      </c>
+      <c r="O14" s="4">
+        <v>239.3929907070693</v>
+      </c>
+      <c r="P14" s="5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4883890944371336</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.05362727280014723</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5113640226572467</v>
+      </c>
+      <c r="K15" s="4">
+        <v>91.25850340136056</v>
+      </c>
+      <c r="L15" s="4">
+        <v>95.16778523489933</v>
+      </c>
+      <c r="M15" s="5">
+        <v>6</v>
+      </c>
+      <c r="N15" s="5">
+        <v>84448.17233085632</v>
+      </c>
+      <c r="O15" s="4">
+        <v>246.9244804995799</v>
+      </c>
+      <c r="P15" s="5">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1598412198175725</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1598412198175725</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1566841207295963</v>
+      </c>
+      <c r="K16" s="4">
+        <v>99.59183673469387</v>
+      </c>
+      <c r="L16" s="4">
+        <v>99.32885906040268</v>
+      </c>
+      <c r="M16" s="5">
+        <v>6</v>
+      </c>
+      <c r="N16" s="5">
+        <v>10614.94994163513</v>
+      </c>
+      <c r="O16" s="4">
+        <v>101.094761348906</v>
+      </c>
+      <c r="P16" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1697269596414387</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1697269596414387</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1885148999846597</v>
+      </c>
+      <c r="K17" s="4">
+        <v>87.85714285714286</v>
+      </c>
+      <c r="L17" s="4">
+        <v>93.69686800894856</v>
+      </c>
+      <c r="M17" s="5">
+        <v>6</v>
+      </c>
+      <c r="N17" s="5">
+        <v>37843.46795082092</v>
+      </c>
+      <c r="O17" s="4">
+        <v>97.78673889101015</v>
+      </c>
+      <c r="P17" s="5">
+        <v>387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3516,9 +5406,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>6</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6174,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6216,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6247,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.476541434065426</v>
@@ -3629,10 +6306,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.476541434065426</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3537798034703132</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3537798034703132</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.08461870433103513</v>
@@ -3670,9 +6365,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08461870433103513</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08461870433103513</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6394,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6413,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6455,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6486,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5190872621757805</v>
@@ -3801,10 +6545,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5190872621757805</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1150118114388026</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5235556197046094</v>
@@ -3842,9 +6602,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5235556197046094</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5235556197046094</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6631,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6650,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6692,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6723,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1731525583425409</v>
@@ -3973,10 +6782,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1731525583425409</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07313402647909072</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07313402647909072</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.718539671909923</v>
@@ -4014,9 +6841,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.718539671909923</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.718539671909923</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6870,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6889,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6931,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6962,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5188883243344733</v>
@@ -4145,10 +7021,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3625029461225623</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3013865566609359</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3013865566609359</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5239676070092969</v>
@@ -4186,9 +7080,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5239676070092969</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5239676070092969</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7109,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7128,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7170,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7201,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1836978061357385</v>
@@ -4317,10 +7260,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1836978061357385</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05461695666250137</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05461695666250137</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6958762574316211</v>
@@ -4358,9 +7319,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6958762574316211</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6958762574316211</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7348,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2791019106613206</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2791019106613206</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2506868935490942</v>
-      </c>
-      <c r="E3" s="4">
-        <v>94.26530612244898</v>
-      </c>
-      <c r="F3" s="4">
-        <v>96.54362416107382</v>
-      </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3384378580340854</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3384378580340854</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6501350968061637</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.06122448979592</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.26845637583892</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.131594308252686</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7342142536621115</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.185978539820069</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.87755102040816</v>
-      </c>
-      <c r="F3" s="4">
-        <v>91.25503355704699</v>
-      </c>
-      <c r="G3" s="5">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5">
-        <v>4</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1624041962743945</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1624041962743945</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2658816743017383</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.85714285714286</v>
-      </c>
-      <c r="F4" s="4">
-        <v>90.1006711409396</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SmithAtmosphere2025.xlsx
+++ b/public/downloads/SmithAtmosphere2025.xlsx
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2791019106613206</v>
+        <v>-0.2757035684902078</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1427294138103753</v>
+        <v>0.1420497453761527</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1427294138103753</v>
+        <v>0.1420497453761527</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -1793,16 +1793,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6661573512712365</v>
+        <v>-0.2646281822204557</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>1.158974505618751</v>
+        <v>1.078668671808594</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9349788381875019</v>
+        <v>0.7342142536621115</v>
       </c>
       <c r="R3" s="5">
         <v>4</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05109513207551118</v>
+        <v>-0.04201734718084538</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08096511075257411</v>
+        <v>0.07914955377364094</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08096511075257411</v>
+        <v>0.07914955377364094</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01502551005688844</v>
+        <v>-0.07515886223998791</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1502649960765655</v>
+        <v>0.1322281216171902</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1502649960765655</v>
+        <v>0.1322281216171902</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0858382327714807</v>
+        <v>-0.08859279549804455</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2120756887406242</v>
+        <v>0.2115247761953114</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2120756887406242</v>
+        <v>0.2115247761953114</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1849022967973596</v>
+        <v>-0.2021631848168965</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09631816026406341</v>
+        <v>0.09286598266015603</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09631816026406341</v>
+        <v>0.09286598266015603</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2988,16 +2988,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.84338024689349</v>
+        <v>-0.8787144525527921</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0686221217753433</v>
+        <v>0.05536855946521087</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0686221217753433</v>
+        <v>0.05536855946521087</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3227,16 +3227,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7854401691118127</v>
+        <v>-0.7749099834442106</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05362727280014723</v>
+        <v>0.05152123566662681</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05362727280014723</v>
+        <v>0.05152123566662681</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3462,16 +3462,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2647695763269312</v>
+        <v>-0.3047669036865202</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1486653125727776</v>
+        <v>0.1406658471008598</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1486653125727776</v>
+        <v>0.1406658471008598</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3701,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6560295684495813</v>
+        <v>-0.6955913408850023</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.114965831009913</v>
+        <v>0.1070534765228288</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.114965831009913</v>
+        <v>0.1070534765228288</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3904,13 +3904,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3089196202804336</v>
+        <v>0.2833918807609024</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3089196202804336</v>
+        <v>0.2833918807609024</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3200325486709366</v>
+        <v>0.2945048091514053</v>
       </c>
       <c r="K3" s="4">
         <v>95.17006802721087</v>
@@ -4004,13 +4004,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3473683007175628</v>
+        <v>0.346988618666862</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3473683007175628</v>
+        <v>0.346988618666862</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3535284646634049</v>
+        <v>0.3539081467141057</v>
       </c>
       <c r="K5" s="4">
         <v>90.62925170068026</v>
@@ -4054,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3384833983856628</v>
+        <v>0.313504902203371</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3384833983856628</v>
+        <v>0.313504902203371</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3553168626902689</v>
+        <v>0.3147087205965171</v>
       </c>
       <c r="K6" s="4">
         <v>88.58843537414965</v>
@@ -4104,13 +4104,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.161493506790688</v>
+        <v>0.155968783484699</v>
       </c>
       <c r="I7" s="4">
-        <v>0.161493506790688</v>
+        <v>0.155968783484699</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1647115218256815</v>
+        <v>0.1598556421069321</v>
       </c>
       <c r="K7" s="4">
         <v>95.52721088435374</v>
@@ -4154,13 +4154,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1753474878476603</v>
+        <v>0.1747810974858082</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1753474878476603</v>
+        <v>0.1747810974858082</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2060518305052728</v>
+        <v>0.2066182208671249</v>
       </c>
       <c r="K8" s="4">
         <v>94.06462585034014</v>
@@ -4204,13 +4204,13 @@
         <v>16.66666666666666</v>
       </c>
       <c r="H9" s="4">
-        <v>0.992879454061358</v>
+        <v>0.9259579258862279</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7804639098048805</v>
+        <v>0.619852242184568</v>
       </c>
       <c r="J9" s="4">
-        <v>1.044232590759763</v>
+        <v>0.9885243651969375</v>
       </c>
       <c r="K9" s="4">
         <v>87.04081632653062</v>
@@ -4254,13 +4254,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.07737330423449412</v>
+        <v>0.07586034008538316</v>
       </c>
       <c r="I10" s="4">
-        <v>0.07737330423449412</v>
+        <v>0.07586034008538316</v>
       </c>
       <c r="J10" s="4">
-        <v>0.08364654040301946</v>
+        <v>0.08515950455213044</v>
       </c>
       <c r="K10" s="4">
         <v>90.5498866213152</v>
@@ -4304,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2850650922683911</v>
+        <v>0.2700343635522451</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2850650922683911</v>
+        <v>0.2700343635522451</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3214945769536532</v>
+        <v>0.3106821086846914</v>
       </c>
       <c r="K11" s="4">
         <v>93.9795918367347</v>
@@ -4354,13 +4354,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.3440207687214316</v>
+        <v>0.343561674933671</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3440207687214316</v>
+        <v>0.343561674933671</v>
       </c>
       <c r="J12" s="4">
-        <v>0.3295948552285931</v>
+        <v>0.3291357614408324</v>
       </c>
       <c r="K12" s="4">
         <v>84.7732426303855</v>
@@ -4404,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1777588047342097</v>
+        <v>0.1748819900642869</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1777588047342097</v>
+        <v>0.1748819900642869</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2116352238015925</v>
+        <v>0.2087584091316697</v>
       </c>
       <c r="K13" s="4">
         <v>93.80952380952381</v>
@@ -4454,13 +4454,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1082630407493735</v>
+        <v>0.09721840549092982</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1082630407493735</v>
+        <v>0.09721840549092982</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1056637417952877</v>
+        <v>0.09425186245216792</v>
       </c>
       <c r="K14" s="4">
         <v>99.89795918367346</v>
@@ -4504,13 +4504,13 @@
         <v>16.66666666666666</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4883890944371336</v>
+        <v>0.4866340634925332</v>
       </c>
       <c r="I15" s="4">
-        <v>0.05362727280014723</v>
+        <v>0.05152123566662681</v>
       </c>
       <c r="J15" s="4">
-        <v>0.5113640226572467</v>
+        <v>0.5120928364697264</v>
       </c>
       <c r="K15" s="4">
         <v>91.25850340136056</v>
@@ -4554,13 +4554,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1598412198175725</v>
+        <v>0.1531749985909743</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1598412198175725</v>
+        <v>0.1531749985909743</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1566841207295963</v>
+        <v>0.1514410796063001</v>
       </c>
       <c r="K16" s="4">
         <v>99.59183673469387</v>
@@ -4604,13 +4604,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1697269596414387</v>
+        <v>0.1631333309022018</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1697269596414387</v>
+        <v>0.1631333309022018</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1885148999846597</v>
+        <v>0.1819212712454229</v>
       </c>
       <c r="K17" s="4">
         <v>87.85714285714286</v>
@@ -6307,16 +6307,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.476541434065426</v>
+        <v>-0.3233749969482389</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3537798034703132</v>
+        <v>0.3231465160468758</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3537798034703132</v>
+        <v>0.3231465160468758</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -6783,16 +6783,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1731525583425409</v>
+        <v>-0.1754306506467458</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07313402647909072</v>
+        <v>0.07267840801824973</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07313402647909072</v>
+        <v>0.07267840801824973</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7022,16 +7022,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3625029461225623</v>
+        <v>0.4437192303100659</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3013865566609359</v>
+        <v>0.2714123612421858</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3013865566609359</v>
+        <v>0.2714123612421858</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7261,16 +7261,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1836978061357385</v>
+        <v>-0.2168461459716724</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05461695666250137</v>
+        <v>0.04798728869531459</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05461695666250137</v>
+        <v>0.04798728869531459</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
